--- a/out/LSTM_Base_repeat_1_000008.xlsx
+++ b/out/LSTM_Base_repeat_1_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.481593977180774</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.481593977180774</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.481593977180774</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.358776160273009</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.958776160273009</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001309930757600814</v>
+        <v>-8.814955669618211e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1504858845091177</v>
+        <v>-0.1012669099610395</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1507437838550194</v>
+        <v>-0.1014331470223259</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4563257889714621</v>
+        <v>0.280784626064627</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7627844707916938</v>
+        <v>0.4606757363498385</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03251311665591503</v>
+        <v>0.0200058822409753</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3707524774976536</v>
+        <v>0.2194519510909577</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05701705702885747</v>
+        <v>0.03508337270451147</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4522625513204825</v>
+        <v>0.2696063947709515</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06926899062906326</v>
+        <v>0.042622466309079</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5337780503465315</v>
+        <v>0.31976435981928</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01833031046867782</v>
+        <v>0.01127882762152322</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5010812424944351</v>
+        <v>0.2996452760272641</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01018341816259477</v>
+        <v>0.006264118489158451</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5031003217257061</v>
+        <v>0.3008857286902564</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02139549778580887</v>
+        <v>0.01316483409892891</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5357225572604134</v>
+        <v>0.320958103300164</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008403484173615553</v>
+        <v>0.005168706523071533</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5311136577189609</v>
+        <v>0.3181203424127828</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005982249854186671</v>
+        <v>0.003679461448730259</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5346728957648005</v>
+        <v>0.3203084030693702</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002352299121195953</v>
+        <v>0.001445227800367095</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5333888581231306</v>
+        <v>0.3195165296815226</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001332946628964219</v>
+        <v>0.0008181146311830566</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5337010786432203</v>
+        <v>0.3197066860844351</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005046762461158673</v>
+        <v>0.0003085565845920197</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5333764149258756</v>
+        <v>0.319505026608557</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002339084162213094</v>
+        <v>0.0001414277389743509</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5333391929694272</v>
+        <v>0.3194802041705244</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5332702743028414</v>
+        <v>0.3194357333050648</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.074052980474707e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5332291838216928</v>
+        <v>0.3194085493913081</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5332241637163579</v>
+        <v>0.3194035367323935</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5332201816317658</v>
+        <v>0.3193991551468328</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.533217746961575</v>
+        <v>0.3193958047920401</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5332122297195853</v>
+        <v>0.3193904354650522</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5332059057255774</v>
+        <v>0.3193844427316219</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.533200537936999</v>
+        <v>0.3193790749430435</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5332005746854906</v>
+        <v>0.3193791116915352</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5332006849309663</v>
+        <v>0.3193792219370107</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5332007584279499</v>
+        <v>0.3193792954339944</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.533200942170409</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5332024856070655</v>
+        <v>0.31938102261311</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5332052049954605</v>
+        <v>0.3193837420015051</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5332065646896579</v>
+        <v>0.3193851016957024</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5332043597801486</v>
+        <v>0.3193828967861931</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5332036615588038</v>
+        <v>0.3193821985648484</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5332033308223775</v>
+        <v>0.319381867828422</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.533203036834443</v>
+        <v>0.3193815738404875</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5332025591040491</v>
+        <v>0.3193810961100936</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5332025223555574</v>
+        <v>0.3193810593616019</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.533202191619131</v>
+        <v>0.3193807286251755</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5332031470799183</v>
+        <v>0.3193816840859628</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5332027795950002</v>
+        <v>0.3193813166010447</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5332032205769022</v>
+        <v>0.3193817575829467</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.533202595852541</v>
+        <v>0.3193811328585855</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5332024121100819</v>
+        <v>0.3193809491161264</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5332020078766718</v>
+        <v>0.3193805448827164</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5332011259128682</v>
+        <v>0.3193796629189127</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5332013096553273</v>
+        <v>0.3193798466613719</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5332016403917538</v>
+        <v>0.3193801773977983</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5332015301462782</v>
+        <v>0.3193800671523228</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5332014933977863</v>
+        <v>0.3193800304038308</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5332014199008026</v>
+        <v>0.3193799569068472</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5332013831523109</v>
+        <v>0.3193799201583555</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5332010891643763</v>
+        <v>0.3193796261704208</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5332010156673926</v>
+        <v>0.3193795526734372</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.533200942170409</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.533201346403819</v>
+        <v>0.3193798834098636</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_1_000008.xlsx
+++ b/out/LSTM_Base_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001309930757600814</v>
+        <v>-0.0001250325101115741</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1504858845091177</v>
+        <v>-0.1436383394110767</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1506168775848778</v>
+        <v>-0.1437633719211883</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1507437838550194</v>
+        <v>-0.1438770184949686</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4563257889714621</v>
+        <v>0.408646940627782</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7627844707916938</v>
+        <v>0.6742019943296244</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03251311665591503</v>
+        <v>0.02911600872188437</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3707524774976536</v>
+        <v>0.3231311156172473</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05701705702885747</v>
+        <v>0.05105968717896519</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4522625513204825</v>
+        <v>0.3961246913681249</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06926899062906326</v>
+        <v>0.0620311780347064</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5337780503465315</v>
+        <v>0.4691231260509682</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01833031046867782</v>
+        <v>0.01641516892444576</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.5010812424944351</v>
+        <v>0.4398424641058559</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01018341816259477</v>
+        <v>0.00911875396224728</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.5031003217257061</v>
+        <v>0.4416500688714332</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02139549778580887</v>
+        <v>0.01916118220860881</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5357225572604134</v>
+        <v>0.4708645359880498</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008403484173615553</v>
+        <v>0.00752424472236323</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.958776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5311136577189609</v>
+        <v>0.4667367159171554</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005982249854186671</v>
+        <v>0.005357823335253921</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5346728957648005</v>
+        <v>0.4699237690919351</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002352299121195953</v>
+        <v>0.002105162923006054</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.20100841007738</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5333888581231306</v>
+        <v>0.4687734566213284</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001332946628964219</v>
+        <v>0.001192678030766358</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5337010786432203</v>
+        <v>0.4690526038938677</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005046762461158673</v>
+        <v>0.0004518296307351898</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5333764149258756</v>
+        <v>0.4687610850320081</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002339084162213094</v>
+        <v>0.0002085863260227374</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5333391929694272</v>
+        <v>0.4687272048089828</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>7.331055355233552e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5332702743028414</v>
+        <v>0.4686647664337412</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.837230183129111e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5332291838216928</v>
+        <v>0.4686273177764935</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5332241637163579</v>
+        <v>0.4686222999050845</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>2.191662034084867e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5332201816317658</v>
+        <v>0.4686182091524974</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.533217746961575</v>
+        <v>0.4686155917490786</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5332122297195853</v>
+        <v>0.4686100745070889</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5332059057255774</v>
+        <v>0.468603750513081</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.533200537936999</v>
+        <v>0.4685983827245026</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5332005746854906</v>
+        <v>0.4685984194729943</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.5332006849309663</v>
+        <v>0.4685985297184698</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5332007584279499</v>
+        <v>0.4685986032154534</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.533200942170409</v>
+        <v>0.4685987869579126</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5332024856070655</v>
+        <v>0.4686003303945691</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.4686018003342421</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5332052049954605</v>
+        <v>0.4686030497829642</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5332065646896579</v>
+        <v>0.4686044094771615</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5332043597801486</v>
+        <v>0.4686022045676522</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5332039555467386</v>
+        <v>0.4686018003342421</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.4686009551189302</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5332036615588038</v>
+        <v>0.4686015063463075</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5332033308223775</v>
+        <v>0.4686011756098811</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.533203036834443</v>
+        <v>0.4686008816219466</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.4686009551189302</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.4686005141370282</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5332025591040491</v>
+        <v>0.4686004038915527</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5332025223555574</v>
+        <v>0.468600367143061</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5332026693495246</v>
+        <v>0.4686005141370282</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.533202191619131</v>
+        <v>0.4686000364066346</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5332031470799183</v>
+        <v>0.4686009918674219</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5332031103314266</v>
+        <v>0.4686009551189302</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8815939771807735</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.5332027795950002</v>
+        <v>0.4686006243825038</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.650235870066816</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5332032205769022</v>
+        <v>0.4686010653644058</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.533202595852541</v>
+        <v>0.4686004406400446</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5332024121100819</v>
+        <v>0.4686002568975854</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5332020078766718</v>
+        <v>0.4685998526641754</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.4685990074488635</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.5332011259128682</v>
+        <v>0.4685989707003718</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.468599117694339</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.4685990441973554</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5332012729068354</v>
+        <v>0.468599117694339</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5332013096553273</v>
+        <v>0.468599154442831</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5332011994098518</v>
+        <v>0.4685990441973554</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5332016403917538</v>
+        <v>0.4685994851792574</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.5332015301462782</v>
+        <v>0.4685993749337818</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5332014933977863</v>
+        <v>0.4685993381852899</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5332014199008026</v>
+        <v>0.4685992646883063</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5332013831523109</v>
+        <v>0.4685992279398146</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5332011626613599</v>
+        <v>0.4685990074488635</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5332010891643763</v>
+        <v>0.4685989339518798</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5332010156673926</v>
+        <v>0.4685988604548962</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668161</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.4685988972033882</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.001008410077380006</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.533200942170409</v>
+        <v>0.4685987869579126</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.958776160273009</v>
+        <v>0.6482190499120561</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5332010524158846</v>
+        <v>0.4685988972033882</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.533201346403819</v>
+        <v>0.4685991911913227</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_1_000008.xlsx
+++ b/out/LSTM_Base_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.02107860520482063</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.01364894863218069</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.0007712598890066147</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.008344253525137901</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.4482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001593079417943954</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.005666585639119148</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.16</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.007127257995307446</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.007510321214795113</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.005273416638374329</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.004510426893830299</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.00230049341917038</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.0007229354232549667</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0002368409186601639</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0009221620857715607</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.004730291664600372</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002099255099892616</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.001338208094239235</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.002828888595104218</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.002885011956095695</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.002212978899478912</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.00174914114177227</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.000806562602519989</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.000179484486579895</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.20100841007738</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001712711527943611</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001475613564252853</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.0009240452200174332</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0001967307180166245</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0005284007638692856</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001764098182320595</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.003107056021690369</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.01115038059651852</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.007133973762392998</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.003403117880225182</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.297446509901492</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002057213336229324</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.097446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0002113450318574905</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001213341951370239</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.0009135734289884567</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0006744116544723511</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.003606945276260376</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.097446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.006759731099009514</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.097446509901492</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.007269641384482384</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.097446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.009998613968491554</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.097446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01692948676645756</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.097446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.02068893052637577</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001250325101115741</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1436383394110767</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.007297931239008904</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0009143631905317307</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.00620553269982338</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.007631227374076843</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00771675817668438</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.006273333914577961</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.004567936062812805</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.00112418457865715</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.000744326040148735</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.002061234787106514</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.297446509901492</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.002449074760079384</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.297446509901492</v>
+        <v>0.3</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.002493759617209435</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.004027148708701134</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1437633719211883</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.009908070787787437</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1438770184949686</v>
+        <v>-0.1339663389616772</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.408646940627782</v>
+        <v>0.3680065402900342</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.006143650040030479</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6742019943296244</v>
+        <v>0.6027538421305714</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02911600872188437</v>
+        <v>0.02622042531677816</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.00353706069290638</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3231311156172473</v>
+        <v>0.2865973152738647</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05105968717896519</v>
+        <v>0.04598156383343387</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.005683260038495064</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.297446509901492</v>
+        <v>0.3</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3961246913681249</v>
+        <v>0.352331524198567</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0620311780347064</v>
+        <v>0.05586216967802747</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.001593859866261482</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4691231260509682</v>
+        <v>0.4180702920359178</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01641516892444576</v>
+        <v>0.01478252973448952</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.003895871341228485</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4398424641058559</v>
+        <v>0.3917015666391195</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.00911875396224728</v>
+        <v>0.008211478094756124</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.005405640229582787</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4416500688714332</v>
+        <v>0.3933289276994308</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01916118220860881</v>
+        <v>0.01725507988516296</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.01099280081689358</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4708645359880498</v>
+        <v>0.4196383949878698</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.00752424472236323</v>
+        <v>0.00677580122253687</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.00853375717997551</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4667367159171554</v>
+        <v>0.4159203703824254</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005357823335253921</v>
+        <v>0.004824818378485358</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.0009151045233011246</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.6482190499120561</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4699237690919351</v>
+        <v>0.418790168995929</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002105162923006054</v>
+        <v>0.001896047678383832</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.002080082893371582</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.20100841007738</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4687734566213284</v>
+        <v>0.4177536870268404</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001192678030766358</v>
+        <v>0.001073989216906629</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.007006807252764702</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4690526038938677</v>
+        <v>0.4180045100269127</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004518296307351898</v>
+        <v>0.0004060292307386027</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.01112917251884937</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4687610850320081</v>
+        <v>0.4177417167064734</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002085863260227374</v>
+        <v>0.0001876680775978301</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.01414461340755224</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4687272048089828</v>
+        <v>0.4177107312577246</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.331055355233552e-05</v>
+        <v>6.523730060879578e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01519056502729654</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4686647664337412</v>
+        <v>0.417654184056432</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.837230183129111e-05</v>
+        <v>1.59873730729961e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01364277396351099</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4686273177764935</v>
+        <v>0.4176200464866587</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01127048768103123</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4686222999050845</v>
+        <v>0.4176150301045338</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006194785237312317</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4686182091524974</v>
+        <v>0.4176108298952114</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004912368021905422</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4686155917490786</v>
+        <v>0.4176078460161057</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.005754368379712105</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4686100745070889</v>
+        <v>0.4176024022710994</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.007372903637588024</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.468603750513081</v>
+        <v>0.417596409537669</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.006485786288976669</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4685983827245026</v>
+        <v>0.4175910417490907</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005510400049388409</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4685984194729943</v>
+        <v>0.4175910784975824</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002851417288184166</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4685985297184698</v>
+        <v>0.4175911887430579</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001676281914114952</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4685986032154534</v>
+        <v>0.4175912622400415</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.005878394469618797</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4685987869579126</v>
+        <v>0.4175914459825007</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.01919134892523289</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4686003303945691</v>
+        <v>0.4175929894191571</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.02390703372657299</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4686018003342421</v>
+        <v>0.4175944593588302</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.02891515009105206</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4686030497829642</v>
+        <v>0.4175957088075523</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0424366220831871</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4686044094771615</v>
+        <v>0.4175970685017495</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.0109995175153017</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6482190499120561</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4686022045676522</v>
+        <v>0.4175948635922402</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01093621551990509</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.001008410077380006</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4686018003342421</v>
+        <v>0.4175944593588302</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.02306422591209412</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4686009551189302</v>
+        <v>0.4175936141435183</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.02871174737811089</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4686015063463075</v>
+        <v>0.4175941653708956</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.02993132919073105</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4686011756098811</v>
+        <v>0.4175938346344691</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.02523563243448734</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4686008816219466</v>
+        <v>0.4175935406465346</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.02446119673550129</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4686009551189302</v>
+        <v>0.4175936141435183</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.02251294627785683</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4686005141370282</v>
+        <v>0.4175931731616163</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01984176784753799</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4686004038915527</v>
+        <v>0.4175930629161408</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01482709776610136</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.468600367143061</v>
+        <v>0.4175930261676491</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01495365798473358</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4686005141370282</v>
+        <v>0.4175931731616163</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.003265278413891792</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4686000364066346</v>
+        <v>0.4175926954312227</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.004972647875547409</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4686009918674219</v>
+        <v>0.4175936508920099</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00576603040099144</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4686009551189302</v>
+        <v>0.4175936141435183</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01257626432925463</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.650235870066816</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4686006243825038</v>
+        <v>0.4175932834070918</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01566828042268753</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.650235870066816</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4686010653644058</v>
+        <v>0.4175937243889938</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01910421811044216</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4686004406400446</v>
+        <v>0.4175930996646327</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0200510285794735</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4686002568975854</v>
+        <v>0.4175929159221735</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02282518334686756</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4685998526641754</v>
+        <v>0.4175925116887635</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.02381881698966026</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4685990074488635</v>
+        <v>0.4175916664734515</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01924205757677555</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4685989707003718</v>
+        <v>0.4175916297249598</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01463961880654097</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.468599117694339</v>
+        <v>0.4175917767189271</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.0106902401894331</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4685990441973554</v>
+        <v>0.4175917032219434</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.002344613894820213</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.468599117694339</v>
+        <v>0.4175917767189271</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.0056218346580863</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.468599154442831</v>
+        <v>0.417591813467419</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002438167110085487</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4685990441973554</v>
+        <v>0.4175917032219434</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003958666697144508</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4685994851792574</v>
+        <v>0.4175921442038454</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003997920081019402</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4685993749337818</v>
+        <v>0.4175920339583699</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005794776603579521</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4685993381852899</v>
+        <v>0.4175919972098779</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.006424557417631149</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4685992646883063</v>
+        <v>0.4175919237128943</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.007384952157735825</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.3</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4685992279398146</v>
+        <v>0.4175918869644026</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.008940421044826508</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4685990074488635</v>
+        <v>0.4175916664734515</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.007036942988634109</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4685989339518798</v>
+        <v>0.4175915929764679</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.006474352441728115</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8502358700668161</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4685988604548962</v>
+        <v>0.4175915194794843</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.00628367718309164</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8502358700668161</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4685988972033882</v>
+        <v>0.4175915562279762</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.003899874165654182</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.001008410077380006</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4685987869579126</v>
+        <v>0.4175914459825007</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
+        <v>0.001914214342832565</v>
+      </c>
+      <c r="JB125" t="n">
         <v>1</v>
       </c>
-      <c r="JB125" t="n">
-        <v>0.6482190499120561</v>
-      </c>
       <c r="JC125" t="n">
-        <v>0.4685988972033882</v>
+        <v>0.4175915562279762</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.004467146471142769</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.297446509901492</v>
+        <v>1.14</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4685991911913227</v>
+        <v>0.4175918502159107</v>
       </c>
     </row>
   </sheetData>
